--- a/_business-operations/sales-forecast/tk6-8月销售计划.xlsx
+++ b/_business-operations/sales-forecast/tk6-8月销售计划.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
-  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10525"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/qisanjiudekeaiduo/Downloads/python3/Harlottecc/_business-operations/sales-forecast/"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{87EE9439-0F3F-824B-BDBC-70FF2083423D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12255"/>
+    <workbookView xWindow="0" yWindow="720" windowWidth="29400" windowHeight="18400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -27,18 +33,19 @@
 </file>
 
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
-<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
     <author>Unknown User</author>
   </authors>
   <commentList>
-    <comment ref="T1" authorId="0">
+    <comment ref="T1" authorId="0" shapeId="0" xr:uid="{00000000-0006-0000-0000-000001000000}">
       <text>
         <r>
           <rPr>
             <sz val="9"/>
             <color rgb="FF000000"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t>=（单位头程+入库费）*销量，单位人民币</t>
@@ -48,6 +55,7 @@
             <sz val="10"/>
             <color rgb="FF000000"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -57,6 +65,7 @@
           <rPr>
             <sz val="10"/>
             <rFont val="宋体"/>
+            <family val="3"/>
             <charset val="134"/>
           </rPr>
           <t xml:space="preserve">
@@ -69,7 +78,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="127" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="122" uniqueCount="47">
   <si>
     <t>部门</t>
   </si>
@@ -220,17 +229,13 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
-  <numFmts count="7">
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="176" formatCode="&quot;US$&quot;#,##0.00;&quot;US$&quot;\-#,##0.00"/>
-    <numFmt numFmtId="177" formatCode="0.00_ "/>
-    <numFmt numFmtId="178" formatCode="0.00_);[Red]\(0.00\)"/>
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="3">
+    <numFmt numFmtId="180" formatCode="&quot;US$&quot;#,##0.00;&quot;US$&quot;\-#,##0.00"/>
+    <numFmt numFmtId="181" formatCode="0.00_ "/>
+    <numFmt numFmtId="182" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
-  <fonts count="27">
+  <fonts count="7">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -242,6 +247,7 @@
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
@@ -249,184 +255,38 @@
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="10"/>
-      <color theme="10"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="等线"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="0"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="等线"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="9"/>
       <color rgb="FF000000"/>
       <name val="宋体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <name val="等线"/>
+      <family val="4"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="42">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -487,194 +347,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="11">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -710,251 +384,9 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="double">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="double">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="double">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="double">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="49">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="9" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="4" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="14" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="10" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="37" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="38" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="39" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="40" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="41" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -965,43 +397,43 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="4" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="176" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="180" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="177" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="181" fontId="2" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="4" fontId="2" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="4" fontId="2" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="182" fontId="2" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1010,7 +442,7 @@
     <xf numFmtId="9" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="9" fontId="2" fillId="6" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -1019,89 +451,45 @@
     <xf numFmtId="0" fontId="1" fillId="8" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="178" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="182" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="9" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="10" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="9" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
-  <cellStyles count="49">
+  <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
-    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
-    <cellStyle name="货币" xfId="2" builtinId="4"/>
-    <cellStyle name="百分比" xfId="3" builtinId="5"/>
-    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
-    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
-    <cellStyle name="超链接" xfId="6" builtinId="8"/>
-    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
-    <cellStyle name="注释" xfId="8" builtinId="10"/>
-    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
-    <cellStyle name="标题" xfId="10" builtinId="15"/>
-    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
-    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
-    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
-    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
-    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
-    <cellStyle name="输入" xfId="16" builtinId="20"/>
-    <cellStyle name="输出" xfId="17" builtinId="21"/>
-    <cellStyle name="计算" xfId="18" builtinId="22"/>
-    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
-    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
-    <cellStyle name="汇总" xfId="21" builtinId="25"/>
-    <cellStyle name="好" xfId="22" builtinId="26"/>
-    <cellStyle name="差" xfId="23" builtinId="27"/>
-    <cellStyle name="适中" xfId="24" builtinId="28"/>
-    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
-    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
-    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
-    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
-    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
-    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
-    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
-    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
-    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
-    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
-    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
-    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
-    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
-    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
-    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
-    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
-    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
-    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
-    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
-    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
-    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
-    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
-    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
-    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1359,41 +747,42 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
+  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
   <dimension ref="A1:AN19"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" customHeight="1"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="14" customHeight="1"/>
   <cols>
-    <col min="1" max="1" width="16.1666666666667" style="1" customWidth="1"/>
+    <col min="1" max="1" width="16.1640625" style="1" customWidth="1"/>
     <col min="2" max="3" width="9" style="1"/>
-    <col min="4" max="4" width="11.25" style="1"/>
-    <col min="5" max="5" width="12.3333333333333" style="1" customWidth="1"/>
+    <col min="4" max="4" width="11.1640625" style="1"/>
+    <col min="5" max="5" width="12.33203125" style="1" customWidth="1"/>
     <col min="6" max="10" width="9" style="1"/>
-    <col min="11" max="11" width="11.8333333333333" style="1"/>
-    <col min="12" max="12" width="10.6666666666667" style="1" customWidth="1"/>
+    <col min="11" max="11" width="11.83203125" style="1"/>
+    <col min="12" max="12" width="10.6640625" style="1" customWidth="1"/>
     <col min="13" max="20" width="9" style="1"/>
-    <col min="21" max="22" width="12.8333333333333" style="1"/>
+    <col min="21" max="22" width="12.83203125" style="1"/>
     <col min="23" max="24" width="9" style="1"/>
-    <col min="25" max="25" width="10.375" style="1"/>
+    <col min="25" max="25" width="10.33203125" style="1"/>
     <col min="26" max="27" width="9" style="1"/>
-    <col min="28" max="28" width="9.375" style="1"/>
+    <col min="28" max="28" width="9.33203125" style="1"/>
     <col min="29" max="29" width="9" style="1"/>
     <col min="30" max="31" width="10.5" style="1"/>
-    <col min="32" max="32" width="12.8333333333333" style="1"/>
+    <col min="32" max="32" width="12.83203125" style="1"/>
     <col min="33" max="33" width="10.5" style="1"/>
     <col min="34" max="35" width="9" style="1"/>
     <col min="36" max="36" width="10.5" style="1"/>
-    <col min="37" max="37" width="12.8333333333333" style="1"/>
+    <col min="37" max="37" width="12.83203125" style="1"/>
     <col min="38" max="40" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" s="1" customFormat="1" ht="39" customHeight="1" spans="1:40">
+    <row r="1" spans="1:40" s="1" customFormat="1" ht="39" customHeight="1">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1509,7 +898,7 @@
       <c r="AM1" s="7"/>
       <c r="AN1" s="7"/>
     </row>
-    <row r="2" ht="14.25" customHeight="1" spans="1:40">
+    <row r="2" spans="1:40" ht="14.25" customHeight="1">
       <c r="A2" s="8" t="s">
         <v>37</v>
       </c>
@@ -1535,18 +924,18 @@
         <v>99.99</v>
       </c>
       <c r="I2" s="13">
-        <f t="shared" ref="I2:I42" si="0">H2*J2</f>
-        <v>679.932</v>
+        <f t="shared" ref="I2:I18" si="0">H2*J2</f>
+        <v>679.9319999999999</v>
       </c>
       <c r="J2" s="14">
         <v>6.8</v>
       </c>
       <c r="K2" s="13">
-        <f t="shared" ref="K2:K42" si="1">H2*G2</f>
+        <f t="shared" ref="K2:K18" si="1">H2*G2</f>
         <v>49995</v>
       </c>
       <c r="L2" s="15">
-        <f t="shared" ref="L2:L42" si="2">K2*J2</f>
+        <f t="shared" ref="L2:L18" si="2">K2*J2</f>
         <v>339966</v>
       </c>
       <c r="M2" s="16">
@@ -1556,93 +945,93 @@
         <v>15</v>
       </c>
       <c r="O2" s="12">
-        <f t="shared" ref="O2:O42" si="3">N2*J2</f>
+        <f t="shared" ref="O2:O18" si="3">N2*J2</f>
         <v>102</v>
       </c>
       <c r="P2" s="15">
-        <f t="shared" ref="P2:P42" si="4">O2*G2</f>
+        <f t="shared" ref="P2:P18" si="4">O2*G2</f>
         <v>51000</v>
       </c>
       <c r="Q2" s="15">
         <v>180</v>
       </c>
       <c r="R2" s="15">
-        <f t="shared" ref="R2:R42" si="5">Q2*G2</f>
+        <f t="shared" ref="R2:R18" si="5">Q2*G2</f>
         <v>90000</v>
       </c>
       <c r="S2" s="17">
-        <f t="shared" ref="S2:S42" si="6">R2/L2</f>
+        <f t="shared" ref="S2:S18" si="6">R2/L2</f>
         <v>0.2647323555885</v>
       </c>
       <c r="T2" s="12">
         <v>40</v>
       </c>
       <c r="U2" s="15">
-        <f t="shared" ref="U2:U42" si="7">T2*G2</f>
+        <f t="shared" ref="U2:U18" si="7">T2*G2</f>
         <v>20000</v>
       </c>
       <c r="V2" s="18">
-        <f t="shared" ref="V2:V42" si="8">U2/L2</f>
-        <v>0.058829412353</v>
+        <f t="shared" ref="V2:V18" si="8">U2/L2</f>
+        <v>5.8829412353000009E-2</v>
       </c>
       <c r="W2" s="16">
         <v>0.06</v>
       </c>
       <c r="X2" s="12">
-        <f t="shared" ref="X2:X42" si="9">K2*W2</f>
+        <f t="shared" ref="X2:X18" si="9">K2*W2</f>
         <v>2999.7</v>
       </c>
       <c r="Y2" s="19">
-        <f t="shared" ref="Y2:Y42" si="10">X2*J2</f>
+        <f t="shared" ref="Y2:Y18" si="10">X2*J2</f>
         <v>20397.96</v>
       </c>
       <c r="Z2" s="16">
         <v>0.05</v>
       </c>
       <c r="AA2" s="12">
-        <f t="shared" ref="AA2:AA42" si="11">Z2*K2</f>
+        <f t="shared" ref="AA2:AA18" si="11">Z2*K2</f>
         <v>2499.75</v>
       </c>
       <c r="AB2" s="15">
-        <f t="shared" ref="AB2:AB42" si="12">AA2*J2</f>
+        <f t="shared" ref="AB2:AB18" si="12">AA2*J2</f>
         <v>16998.3</v>
       </c>
       <c r="AC2" s="12">
         <v>5000</v>
       </c>
       <c r="AD2" s="15">
-        <f t="shared" ref="AD2:AD42" si="13">AC2*J2</f>
+        <f t="shared" ref="AD2:AD18" si="13">AC2*J2</f>
         <v>34000</v>
       </c>
       <c r="AE2" s="15">
-        <f t="shared" ref="AE2:AE42" si="14">L2-P2-R2-U2-Y2-AB2</f>
-        <v>141569.74</v>
+        <f t="shared" ref="AE2:AE18" si="14">L2-P2-R2-U2-Y2-AB2</f>
+        <v>141569.74000000002</v>
       </c>
       <c r="AF2" s="18">
-        <f t="shared" ref="AF2:AF42" si="15">AE2/L2</f>
-        <v>0.41642323055835</v>
+        <f t="shared" ref="AF2:AF18" si="15">AE2/L2</f>
+        <v>0.41642323055835001</v>
       </c>
       <c r="AG2" s="12">
         <v>20</v>
       </c>
       <c r="AH2" s="12">
-        <f t="shared" ref="AH2:AH42" si="16">AG2*J2</f>
+        <f t="shared" ref="AH2:AH18" si="16">AG2*J2</f>
         <v>136</v>
       </c>
       <c r="AI2" s="12">
-        <f t="shared" ref="AI2:AI42" si="17">AH2*G2</f>
+        <f t="shared" ref="AI2:AI18" si="17">AH2*G2</f>
         <v>68000</v>
       </c>
       <c r="AJ2" s="12">
-        <f t="shared" ref="AJ2:AJ42" si="18">AE2-AI2</f>
-        <v>73569.74</v>
+        <f t="shared" ref="AJ2:AJ18" si="18">AE2-AI2</f>
+        <v>73569.74000000002</v>
       </c>
       <c r="AK2" s="18">
-        <f t="shared" ref="AK2:AK42" si="19">AJ2/L2</f>
+        <f t="shared" ref="AK2:AK18" si="19">AJ2/L2</f>
         <v>0.21640322855815</v>
       </c>
     </row>
-    <row r="3" ht="14.25" customHeight="1" spans="1:40">
+    <row r="3" spans="1:40" ht="14.25" customHeight="1">
       <c r="A3" s="8" t="s">
         <v>37</v>
       </c>
@@ -1669,7 +1058,7 @@
       </c>
       <c r="I3" s="13">
         <f t="shared" si="0"/>
-        <v>679.932</v>
+        <v>679.9319999999999</v>
       </c>
       <c r="J3" s="14">
         <v>6.8</v>
@@ -1716,7 +1105,7 @@
       </c>
       <c r="V3" s="18">
         <f t="shared" si="8"/>
-        <v>0.058829412353</v>
+        <v>5.8829412353000009E-2</v>
       </c>
       <c r="W3" s="16">
         <v>0.06</v>
@@ -1727,7 +1116,7 @@
       </c>
       <c r="Y3" s="19">
         <f t="shared" si="10"/>
-        <v>40795.92</v>
+        <v>40795.919999999998</v>
       </c>
       <c r="Z3" s="16">
         <v>0.05</v>
@@ -1749,11 +1138,11 @@
       </c>
       <c r="AE3" s="15">
         <f t="shared" si="14"/>
-        <v>283139.48</v>
+        <v>283139.48000000004</v>
       </c>
       <c r="AF3" s="18">
         <f t="shared" si="15"/>
-        <v>0.41642323055835</v>
+        <v>0.41642323055835001</v>
       </c>
       <c r="AG3" s="12">
         <v>20</v>
@@ -1768,14 +1157,14 @@
       </c>
       <c r="AJ3" s="12">
         <f t="shared" si="18"/>
-        <v>147139.48</v>
+        <v>147139.48000000004</v>
       </c>
       <c r="AK3" s="18">
         <f t="shared" si="19"/>
         <v>0.21640322855815</v>
       </c>
     </row>
-    <row r="4" ht="19" customHeight="1" spans="1:40">
+    <row r="4" spans="1:40" ht="19" customHeight="1">
       <c r="A4" s="8" t="s">
         <v>37</v>
       </c>
@@ -1802,7 +1191,7 @@
       </c>
       <c r="I4" s="13">
         <f t="shared" si="0"/>
-        <v>679.932</v>
+        <v>679.9319999999999</v>
       </c>
       <c r="J4" s="14">
         <v>6.8</v>
@@ -1838,7 +1227,7 @@
       </c>
       <c r="S4" s="17">
         <f t="shared" si="6"/>
-        <v>0.26179088497085</v>
+        <v>0.26179088497085001</v>
       </c>
       <c r="T4" s="12">
         <v>40</v>
@@ -1849,7 +1238,7 @@
       </c>
       <c r="V4" s="18">
         <f t="shared" si="8"/>
-        <v>0.058829412353</v>
+        <v>5.8829412353000002E-2</v>
       </c>
       <c r="W4" s="16">
         <v>0.06</v>
@@ -1867,11 +1256,11 @@
       </c>
       <c r="AA4" s="12">
         <f t="shared" si="11"/>
-        <v>1499.85</v>
+        <v>1499.8500000000001</v>
       </c>
       <c r="AB4" s="15">
         <f t="shared" si="12"/>
-        <v>10198.98</v>
+        <v>10198.980000000001</v>
       </c>
       <c r="AC4" s="12">
         <v>5000</v>
@@ -1882,7 +1271,7 @@
       </c>
       <c r="AE4" s="15">
         <f t="shared" si="14"/>
-        <v>85541.844</v>
+        <v>85541.844000000012</v>
       </c>
       <c r="AF4" s="18">
         <f t="shared" si="15"/>
@@ -1901,14 +1290,14 @@
       </c>
       <c r="AJ4" s="12">
         <f t="shared" si="18"/>
-        <v>44741.844</v>
+        <v>44741.844000000012</v>
       </c>
       <c r="AK4" s="18">
         <f t="shared" si="19"/>
-        <v>0.2193446991758</v>
+        <v>0.21934469917579999</v>
       </c>
     </row>
-    <row r="5" ht="19" customHeight="1" spans="1:40">
+    <row r="5" spans="1:40" ht="19" customHeight="1">
       <c r="A5" s="8" t="s">
         <v>37</v>
       </c>
@@ -1935,7 +1324,7 @@
       </c>
       <c r="I5" s="13">
         <f t="shared" si="0"/>
-        <v>679.932</v>
+        <v>679.9319999999999</v>
       </c>
       <c r="J5" s="14">
         <v>6.8</v>
@@ -1971,7 +1360,7 @@
       </c>
       <c r="S5" s="17">
         <f t="shared" si="6"/>
-        <v>0.26179088497085</v>
+        <v>0.26179088497085001</v>
       </c>
       <c r="T5" s="12">
         <v>40</v>
@@ -1982,29 +1371,29 @@
       </c>
       <c r="V5" s="18">
         <f t="shared" si="8"/>
-        <v>0.058829412353</v>
+        <v>5.8829412353000009E-2</v>
       </c>
       <c r="W5" s="16">
         <v>0.06</v>
       </c>
       <c r="X5" s="12">
         <f t="shared" si="9"/>
-        <v>1199.88</v>
+        <v>1199.8799999999999</v>
       </c>
       <c r="Y5" s="19">
         <f t="shared" si="10"/>
-        <v>8159.184</v>
+        <v>8159.1839999999993</v>
       </c>
       <c r="Z5" s="16">
         <v>0.05</v>
       </c>
       <c r="AA5" s="12">
         <f t="shared" si="11"/>
-        <v>999.9</v>
+        <v>999.90000000000009</v>
       </c>
       <c r="AB5" s="15">
         <f t="shared" si="12"/>
-        <v>6799.32</v>
+        <v>6799.3200000000006</v>
       </c>
       <c r="AC5" s="12">
         <v>5000</v>
@@ -2015,11 +1404,11 @@
       </c>
       <c r="AE5" s="15">
         <f t="shared" si="14"/>
-        <v>57027.896</v>
+        <v>57027.895999999993</v>
       </c>
       <c r="AF5" s="18">
         <f t="shared" si="15"/>
-        <v>0.419364701176</v>
+        <v>0.41936470117599994</v>
       </c>
       <c r="AG5" s="12">
         <v>20</v>
@@ -2034,14 +1423,14 @@
       </c>
       <c r="AJ5" s="12">
         <f t="shared" si="18"/>
-        <v>29827.896</v>
+        <v>29827.895999999993</v>
       </c>
       <c r="AK5" s="18">
         <f t="shared" si="19"/>
-        <v>0.2193446991758</v>
+        <v>0.21934469917579991</v>
       </c>
     </row>
-    <row r="6" ht="19" customHeight="1" spans="1:40">
+    <row r="6" spans="1:40" ht="23" customHeight="1">
       <c r="A6" s="8" t="s">
         <v>37</v>
       </c>
@@ -2051,8 +1440,8 @@
       <c r="C6" s="8">
         <v>6</v>
       </c>
-      <c r="D6" s="20" t="s">
-        <v>45</v>
+      <c r="D6" s="9" t="s">
+        <v>46</v>
       </c>
       <c r="E6" s="10" t="s">
         <v>40</v>
@@ -2061,251 +1450,251 @@
         <v>41</v>
       </c>
       <c r="G6" s="11">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="H6" s="12">
-        <v>99.99</v>
+        <v>59.99</v>
       </c>
       <c r="I6" s="13">
         <f t="shared" si="0"/>
-        <v>679.932</v>
+        <v>407.93200000000002</v>
       </c>
       <c r="J6" s="14">
         <v>6.8</v>
       </c>
       <c r="K6" s="13">
         <f t="shared" si="1"/>
-        <v>4999.5</v>
+        <v>599.9</v>
       </c>
       <c r="L6" s="15">
         <f t="shared" si="2"/>
-        <v>33996.6</v>
+        <v>4079.3199999999997</v>
       </c>
       <c r="M6" s="16">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
       <c r="N6" s="12">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="O6" s="12">
         <f t="shared" si="3"/>
-        <v>102</v>
+        <v>54.4</v>
       </c>
       <c r="P6" s="15">
         <f t="shared" si="4"/>
-        <v>5100</v>
+        <v>544</v>
       </c>
       <c r="Q6" s="15">
-        <v>178</v>
+        <v>135</v>
       </c>
       <c r="R6" s="15">
         <f t="shared" si="5"/>
-        <v>8900</v>
+        <v>1350</v>
       </c>
       <c r="S6" s="17">
         <f t="shared" si="6"/>
-        <v>0.26179088497085</v>
+        <v>0.33093750919270859</v>
       </c>
       <c r="T6" s="12">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="U6" s="15">
         <f t="shared" si="7"/>
-        <v>2000</v>
+        <v>190</v>
       </c>
       <c r="V6" s="18">
         <f t="shared" si="8"/>
-        <v>0.058829412353</v>
+        <v>4.6576390182677507E-2</v>
       </c>
       <c r="W6" s="16">
         <v>0.06</v>
       </c>
       <c r="X6" s="12">
         <f t="shared" si="9"/>
-        <v>299.97</v>
+        <v>35.994</v>
       </c>
       <c r="Y6" s="19">
         <f t="shared" si="10"/>
-        <v>2039.796</v>
+        <v>244.75919999999999</v>
       </c>
       <c r="Z6" s="16">
         <v>0.05</v>
       </c>
       <c r="AA6" s="12">
         <f t="shared" si="11"/>
-        <v>249.975</v>
+        <v>29.995000000000001</v>
       </c>
       <c r="AB6" s="15">
         <f t="shared" si="12"/>
-        <v>1699.83</v>
+        <v>203.96600000000001</v>
       </c>
       <c r="AC6" s="12">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="AD6" s="15">
         <f t="shared" si="13"/>
-        <v>34000</v>
+        <v>0</v>
       </c>
       <c r="AE6" s="15">
         <f t="shared" si="14"/>
-        <v>14256.974</v>
+        <v>1546.5947999999999</v>
       </c>
       <c r="AF6" s="18">
         <f t="shared" si="15"/>
-        <v>0.419364701176</v>
-      </c>
-      <c r="AG6" s="12">
-        <v>20</v>
-      </c>
+        <v>0.37913054136473723</v>
+      </c>
+      <c r="AG6" s="12"/>
       <c r="AH6" s="12">
         <f t="shared" si="16"/>
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="AI6" s="12">
         <f t="shared" si="17"/>
-        <v>6800</v>
+        <v>0</v>
       </c>
       <c r="AJ6" s="12">
         <f t="shared" si="18"/>
-        <v>7456.974</v>
+        <v>1546.5947999999999</v>
       </c>
       <c r="AK6" s="18">
         <f t="shared" si="19"/>
-        <v>0.2193446991758</v>
+        <v>0.37913054136473723</v>
       </c>
     </row>
-    <row r="7" ht="23" customHeight="1" spans="1:40">
-      <c r="A7" s="8" t="s">
+    <row r="7" spans="1:40" s="1" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A7" s="1" t="s">
         <v>37</v>
       </c>
-      <c r="B7" s="8" t="s">
+      <c r="B7" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="C7" s="8">
-        <v>6</v>
-      </c>
-      <c r="D7" s="9" t="s">
-        <v>46</v>
-      </c>
-      <c r="E7" s="10" t="s">
+      <c r="C7" s="1">
+        <v>7</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="E7" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="F7" s="21" t="s">
         <v>41</v>
       </c>
       <c r="G7" s="11">
-        <v>10</v>
-      </c>
-      <c r="H7" s="12">
-        <v>59.99</v>
-      </c>
-      <c r="I7" s="13">
+        <v>500</v>
+      </c>
+      <c r="H7" s="1">
+        <v>99.99</v>
+      </c>
+      <c r="I7" s="22">
         <f t="shared" si="0"/>
-        <v>407.932</v>
-      </c>
-      <c r="J7" s="14">
+        <v>679.9319999999999</v>
+      </c>
+      <c r="J7" s="23">
         <v>6.8</v>
       </c>
-      <c r="K7" s="13">
+      <c r="K7" s="22">
         <f t="shared" si="1"/>
-        <v>599.9</v>
-      </c>
-      <c r="L7" s="15">
+        <v>49995</v>
+      </c>
+      <c r="L7" s="1">
         <f t="shared" si="2"/>
-        <v>4079.32</v>
-      </c>
-      <c r="M7" s="16">
-        <v>0.15</v>
-      </c>
-      <c r="N7" s="12">
-        <v>8</v>
-      </c>
-      <c r="O7" s="12">
+        <v>339966</v>
+      </c>
+      <c r="M7" s="24">
+        <v>0.05</v>
+      </c>
+      <c r="N7" s="1">
+        <v>15</v>
+      </c>
+      <c r="O7" s="1">
         <f t="shared" si="3"/>
-        <v>54.4</v>
-      </c>
-      <c r="P7" s="15">
+        <v>102</v>
+      </c>
+      <c r="P7" s="1">
         <f t="shared" si="4"/>
-        <v>544</v>
-      </c>
-      <c r="Q7" s="15">
-        <v>135</v>
-      </c>
-      <c r="R7" s="15">
+        <v>51000</v>
+      </c>
+      <c r="Q7" s="1">
+        <v>180</v>
+      </c>
+      <c r="R7" s="1">
         <f t="shared" si="5"/>
-        <v>1350</v>
-      </c>
-      <c r="S7" s="17">
+        <v>90000</v>
+      </c>
+      <c r="S7" s="25">
         <f t="shared" si="6"/>
-        <v>0.330937509192709</v>
-      </c>
-      <c r="T7" s="12">
-        <v>19</v>
-      </c>
-      <c r="U7" s="15">
+        <v>0.2647323555885</v>
+      </c>
+      <c r="T7" s="1">
+        <v>40</v>
+      </c>
+      <c r="U7" s="1">
         <f t="shared" si="7"/>
-        <v>190</v>
-      </c>
-      <c r="V7" s="18">
+        <v>20000</v>
+      </c>
+      <c r="V7" s="26">
         <f t="shared" si="8"/>
-        <v>0.0465763901826775</v>
-      </c>
-      <c r="W7" s="16">
+        <v>5.8829412353000009E-2</v>
+      </c>
+      <c r="W7" s="24">
         <v>0.06</v>
       </c>
-      <c r="X7" s="12">
+      <c r="X7" s="1">
         <f t="shared" si="9"/>
-        <v>35.994</v>
-      </c>
-      <c r="Y7" s="19">
+        <v>2999.7</v>
+      </c>
+      <c r="Y7" s="1">
         <f t="shared" si="10"/>
-        <v>244.7592</v>
-      </c>
-      <c r="Z7" s="16">
+        <v>20397.96</v>
+      </c>
+      <c r="Z7" s="24">
         <v>0.05</v>
       </c>
-      <c r="AA7" s="12">
+      <c r="AA7" s="1">
         <f t="shared" si="11"/>
-        <v>29.995</v>
-      </c>
-      <c r="AB7" s="15">
+        <v>2499.75</v>
+      </c>
+      <c r="AB7" s="1">
         <f t="shared" si="12"/>
-        <v>203.966</v>
-      </c>
-      <c r="AC7" s="12">
-        <v>0</v>
-      </c>
-      <c r="AD7" s="15">
+        <v>16998.3</v>
+      </c>
+      <c r="AC7" s="1">
+        <v>5000</v>
+      </c>
+      <c r="AD7" s="1">
         <f t="shared" si="13"/>
-        <v>0</v>
-      </c>
-      <c r="AE7" s="15">
+        <v>34000</v>
+      </c>
+      <c r="AE7" s="1">
         <f t="shared" si="14"/>
-        <v>1546.5948</v>
-      </c>
-      <c r="AF7" s="18">
+        <v>141569.74000000002</v>
+      </c>
+      <c r="AF7" s="26">
         <f t="shared" si="15"/>
-        <v>0.379130541364737</v>
-      </c>
-      <c r="AG7" s="12"/>
-      <c r="AH7" s="12">
+        <v>0.41642323055835001</v>
+      </c>
+      <c r="AG7" s="1">
+        <v>20</v>
+      </c>
+      <c r="AH7" s="1">
         <f t="shared" si="16"/>
-        <v>0</v>
-      </c>
-      <c r="AI7" s="12">
+        <v>136</v>
+      </c>
+      <c r="AI7" s="1">
         <f t="shared" si="17"/>
-        <v>0</v>
-      </c>
-      <c r="AJ7" s="12">
+        <v>68000</v>
+      </c>
+      <c r="AJ7" s="1">
         <f t="shared" si="18"/>
-        <v>1546.5948</v>
-      </c>
-      <c r="AK7" s="18">
+        <v>73569.74000000002</v>
+      </c>
+      <c r="AK7" s="26">
         <f t="shared" si="19"/>
-        <v>0.379130541364737</v>
+        <v>0.21640322855815</v>
       </c>
     </row>
-    <row r="8" s="1" customFormat="1" ht="14.25" customHeight="1" spans="1:40">
+    <row r="8" spans="1:40" s="1" customFormat="1" ht="14.25" customHeight="1">
       <c r="A8" s="1" t="s">
         <v>37</v>
       </c>
@@ -2316,7 +1705,7 @@
         <v>7</v>
       </c>
       <c r="D8" s="10" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E8" s="21" t="s">
         <v>40</v>
@@ -2325,25 +1714,25 @@
         <v>41</v>
       </c>
       <c r="G8" s="11">
-        <v>500</v>
+        <v>1000</v>
       </c>
       <c r="H8" s="1">
         <v>99.99</v>
       </c>
       <c r="I8" s="22">
         <f t="shared" si="0"/>
-        <v>679.932</v>
+        <v>679.9319999999999</v>
       </c>
       <c r="J8" s="23">
         <v>6.8</v>
       </c>
       <c r="K8" s="22">
         <f t="shared" si="1"/>
-        <v>49995</v>
+        <v>99990</v>
       </c>
       <c r="L8" s="1">
         <f t="shared" si="2"/>
-        <v>339966</v>
+        <v>679932</v>
       </c>
       <c r="M8" s="24">
         <v>0.05</v>
@@ -2357,14 +1746,14 @@
       </c>
       <c r="P8" s="1">
         <f t="shared" si="4"/>
-        <v>51000</v>
+        <v>102000</v>
       </c>
       <c r="Q8" s="1">
         <v>180</v>
       </c>
       <c r="R8" s="1">
         <f t="shared" si="5"/>
-        <v>90000</v>
+        <v>180000</v>
       </c>
       <c r="S8" s="25">
         <f t="shared" si="6"/>
@@ -2375,33 +1764,33 @@
       </c>
       <c r="U8" s="1">
         <f t="shared" si="7"/>
-        <v>20000</v>
+        <v>40000</v>
       </c>
       <c r="V8" s="26">
         <f t="shared" si="8"/>
-        <v>0.058829412353</v>
+        <v>5.8829412353000009E-2</v>
       </c>
       <c r="W8" s="24">
         <v>0.06</v>
       </c>
       <c r="X8" s="1">
         <f t="shared" si="9"/>
-        <v>2999.7</v>
+        <v>5999.4</v>
       </c>
       <c r="Y8" s="1">
         <f t="shared" si="10"/>
-        <v>20397.96</v>
+        <v>40795.919999999998</v>
       </c>
       <c r="Z8" s="24">
         <v>0.05</v>
       </c>
       <c r="AA8" s="1">
         <f t="shared" si="11"/>
-        <v>2499.75</v>
+        <v>4999.5</v>
       </c>
       <c r="AB8" s="1">
         <f t="shared" si="12"/>
-        <v>16998.3</v>
+        <v>33996.6</v>
       </c>
       <c r="AC8" s="1">
         <v>5000</v>
@@ -2412,11 +1801,11 @@
       </c>
       <c r="AE8" s="1">
         <f t="shared" si="14"/>
-        <v>141569.74</v>
+        <v>283139.48000000004</v>
       </c>
       <c r="AF8" s="26">
         <f t="shared" si="15"/>
-        <v>0.41642323055835</v>
+        <v>0.41642323055835001</v>
       </c>
       <c r="AG8" s="1">
         <v>20</v>
@@ -2427,18 +1816,18 @@
       </c>
       <c r="AI8" s="1">
         <f t="shared" si="17"/>
-        <v>68000</v>
+        <v>136000</v>
       </c>
       <c r="AJ8" s="1">
         <f t="shared" si="18"/>
-        <v>73569.74</v>
+        <v>147139.48000000004</v>
       </c>
       <c r="AK8" s="26">
         <f t="shared" si="19"/>
         <v>0.21640322855815</v>
       </c>
     </row>
-    <row r="9" s="1" customFormat="1" ht="14.25" customHeight="1" spans="1:40">
+    <row r="9" spans="1:40" s="1" customFormat="1" ht="19" customHeight="1">
       <c r="A9" s="1" t="s">
         <v>37</v>
       </c>
@@ -2449,7 +1838,7 @@
         <v>7</v>
       </c>
       <c r="D9" s="10" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E9" s="21" t="s">
         <v>40</v>
@@ -2458,25 +1847,25 @@
         <v>41</v>
       </c>
       <c r="G9" s="11">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="H9" s="1">
         <v>99.99</v>
       </c>
       <c r="I9" s="22">
         <f t="shared" si="0"/>
-        <v>679.932</v>
+        <v>679.9319999999999</v>
       </c>
       <c r="J9" s="23">
         <v>6.8</v>
       </c>
       <c r="K9" s="22">
         <f t="shared" si="1"/>
-        <v>99990</v>
+        <v>19998</v>
       </c>
       <c r="L9" s="1">
         <f t="shared" si="2"/>
-        <v>679932</v>
+        <v>135986.4</v>
       </c>
       <c r="M9" s="24">
         <v>0.05</v>
@@ -2490,51 +1879,51 @@
       </c>
       <c r="P9" s="1">
         <f t="shared" si="4"/>
-        <v>102000</v>
+        <v>20400</v>
       </c>
       <c r="Q9" s="1">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="R9" s="1">
         <f t="shared" si="5"/>
-        <v>180000</v>
+        <v>35600</v>
       </c>
       <c r="S9" s="25">
         <f t="shared" si="6"/>
-        <v>0.2647323555885</v>
+        <v>0.26179088497085001</v>
       </c>
       <c r="T9" s="1">
         <v>40</v>
       </c>
       <c r="U9" s="1">
         <f t="shared" si="7"/>
-        <v>40000</v>
+        <v>8000</v>
       </c>
       <c r="V9" s="26">
         <f t="shared" si="8"/>
-        <v>0.058829412353</v>
+        <v>5.8829412353000009E-2</v>
       </c>
       <c r="W9" s="24">
         <v>0.06</v>
       </c>
       <c r="X9" s="1">
         <f t="shared" si="9"/>
-        <v>5999.4</v>
+        <v>1199.8799999999999</v>
       </c>
       <c r="Y9" s="1">
         <f t="shared" si="10"/>
-        <v>40795.92</v>
+        <v>8159.1839999999993</v>
       </c>
       <c r="Z9" s="24">
         <v>0.05</v>
       </c>
       <c r="AA9" s="1">
         <f t="shared" si="11"/>
-        <v>4999.5</v>
+        <v>999.90000000000009</v>
       </c>
       <c r="AB9" s="1">
         <f t="shared" si="12"/>
-        <v>33996.6</v>
+        <v>6799.3200000000006</v>
       </c>
       <c r="AC9" s="1">
         <v>5000</v>
@@ -2545,11 +1934,11 @@
       </c>
       <c r="AE9" s="1">
         <f t="shared" si="14"/>
-        <v>283139.48</v>
+        <v>57027.895999999993</v>
       </c>
       <c r="AF9" s="26">
         <f t="shared" si="15"/>
-        <v>0.41642323055835</v>
+        <v>0.41936470117599994</v>
       </c>
       <c r="AG9" s="1">
         <v>20</v>
@@ -2560,18 +1949,18 @@
       </c>
       <c r="AI9" s="1">
         <f t="shared" si="17"/>
-        <v>136000</v>
+        <v>27200</v>
       </c>
       <c r="AJ9" s="1">
         <f t="shared" si="18"/>
-        <v>147139.48</v>
+        <v>29827.895999999993</v>
       </c>
       <c r="AK9" s="26">
         <f t="shared" si="19"/>
-        <v>0.21640322855815</v>
+        <v>0.21934469917579991</v>
       </c>
     </row>
-    <row r="10" s="1" customFormat="1" ht="19" customHeight="1" spans="1:40">
+    <row r="10" spans="1:40" s="1" customFormat="1" ht="19" customHeight="1">
       <c r="A10" s="1" t="s">
         <v>37</v>
       </c>
@@ -2582,7 +1971,7 @@
         <v>7</v>
       </c>
       <c r="D10" s="10" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E10" s="21" t="s">
         <v>40</v>
@@ -2591,25 +1980,25 @@
         <v>41</v>
       </c>
       <c r="G10" s="11">
-        <v>200</v>
+        <v>400</v>
       </c>
       <c r="H10" s="1">
         <v>99.99</v>
       </c>
       <c r="I10" s="22">
         <f t="shared" si="0"/>
-        <v>679.932</v>
+        <v>679.9319999999999</v>
       </c>
       <c r="J10" s="23">
         <v>6.8</v>
       </c>
       <c r="K10" s="22">
         <f t="shared" si="1"/>
-        <v>19998</v>
+        <v>39996</v>
       </c>
       <c r="L10" s="1">
         <f t="shared" si="2"/>
-        <v>135986.4</v>
+        <v>271972.8</v>
       </c>
       <c r="M10" s="24">
         <v>0.05</v>
@@ -2623,51 +2012,51 @@
       </c>
       <c r="P10" s="1">
         <f t="shared" si="4"/>
-        <v>20400</v>
+        <v>40800</v>
       </c>
       <c r="Q10" s="1">
         <v>178</v>
       </c>
       <c r="R10" s="1">
         <f t="shared" si="5"/>
-        <v>35600</v>
+        <v>71200</v>
       </c>
       <c r="S10" s="25">
         <f t="shared" si="6"/>
-        <v>0.26179088497085</v>
+        <v>0.26179088497085001</v>
       </c>
       <c r="T10" s="1">
         <v>40</v>
       </c>
       <c r="U10" s="1">
         <f t="shared" si="7"/>
-        <v>8000</v>
+        <v>16000</v>
       </c>
       <c r="V10" s="26">
         <f t="shared" si="8"/>
-        <v>0.058829412353</v>
+        <v>5.8829412353000009E-2</v>
       </c>
       <c r="W10" s="24">
         <v>0.06</v>
       </c>
       <c r="X10" s="1">
         <f t="shared" si="9"/>
-        <v>1199.88</v>
+        <v>2399.7599999999998</v>
       </c>
       <c r="Y10" s="1">
         <f t="shared" si="10"/>
-        <v>8159.184</v>
+        <v>16318.367999999999</v>
       </c>
       <c r="Z10" s="24">
         <v>0.05</v>
       </c>
       <c r="AA10" s="1">
         <f t="shared" si="11"/>
-        <v>999.9</v>
+        <v>1999.8000000000002</v>
       </c>
       <c r="AB10" s="1">
         <f t="shared" si="12"/>
-        <v>6799.32</v>
+        <v>13598.640000000001</v>
       </c>
       <c r="AC10" s="1">
         <v>5000</v>
@@ -2678,11 +2067,11 @@
       </c>
       <c r="AE10" s="1">
         <f t="shared" si="14"/>
-        <v>57027.896</v>
+        <v>114055.79199999999</v>
       </c>
       <c r="AF10" s="26">
         <f t="shared" si="15"/>
-        <v>0.419364701176</v>
+        <v>0.41936470117599994</v>
       </c>
       <c r="AG10" s="1">
         <v>20</v>
@@ -2693,18 +2082,18 @@
       </c>
       <c r="AI10" s="1">
         <f t="shared" si="17"/>
-        <v>27200</v>
+        <v>54400</v>
       </c>
       <c r="AJ10" s="1">
         <f t="shared" si="18"/>
-        <v>29827.896</v>
+        <v>59655.791999999987</v>
       </c>
       <c r="AK10" s="26">
         <f t="shared" si="19"/>
-        <v>0.2193446991758</v>
+        <v>0.21934469917579991</v>
       </c>
     </row>
-    <row r="11" s="1" customFormat="1" ht="19" customHeight="1" spans="1:40">
+    <row r="11" spans="1:40" s="1" customFormat="1" ht="19" customHeight="1">
       <c r="A11" s="1" t="s">
         <v>37</v>
       </c>
@@ -2715,7 +2104,7 @@
         <v>7</v>
       </c>
       <c r="D11" s="10" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="E11" s="21" t="s">
         <v>40</v>
@@ -2724,25 +2113,25 @@
         <v>41</v>
       </c>
       <c r="G11" s="11">
-        <v>400</v>
+        <v>100</v>
       </c>
       <c r="H11" s="1">
         <v>99.99</v>
       </c>
       <c r="I11" s="22">
         <f t="shared" si="0"/>
-        <v>679.932</v>
+        <v>679.9319999999999</v>
       </c>
       <c r="J11" s="23">
         <v>6.8</v>
       </c>
       <c r="K11" s="22">
         <f t="shared" si="1"/>
-        <v>39996</v>
+        <v>9999</v>
       </c>
       <c r="L11" s="1">
         <f t="shared" si="2"/>
-        <v>271972.8</v>
+        <v>67993.2</v>
       </c>
       <c r="M11" s="24">
         <v>0.05</v>
@@ -2756,51 +2145,51 @@
       </c>
       <c r="P11" s="1">
         <f t="shared" si="4"/>
-        <v>40800</v>
+        <v>10200</v>
       </c>
       <c r="Q11" s="1">
         <v>178</v>
       </c>
       <c r="R11" s="1">
         <f t="shared" si="5"/>
-        <v>71200</v>
+        <v>17800</v>
       </c>
       <c r="S11" s="25">
         <f t="shared" si="6"/>
-        <v>0.26179088497085</v>
+        <v>0.26179088497085001</v>
       </c>
       <c r="T11" s="1">
         <v>40</v>
       </c>
       <c r="U11" s="1">
         <f t="shared" si="7"/>
-        <v>16000</v>
+        <v>4000</v>
       </c>
       <c r="V11" s="26">
         <f t="shared" si="8"/>
-        <v>0.058829412353</v>
+        <v>5.8829412353000009E-2</v>
       </c>
       <c r="W11" s="24">
         <v>0.06</v>
       </c>
       <c r="X11" s="1">
         <f t="shared" si="9"/>
-        <v>2399.76</v>
+        <v>599.93999999999994</v>
       </c>
       <c r="Y11" s="1">
         <f t="shared" si="10"/>
-        <v>16318.368</v>
+        <v>4079.5919999999996</v>
       </c>
       <c r="Z11" s="24">
         <v>0.05</v>
       </c>
       <c r="AA11" s="1">
         <f t="shared" si="11"/>
-        <v>1999.8</v>
+        <v>499.95000000000005</v>
       </c>
       <c r="AB11" s="1">
         <f t="shared" si="12"/>
-        <v>13598.64</v>
+        <v>3399.6600000000003</v>
       </c>
       <c r="AC11" s="1">
         <v>5000</v>
@@ -2811,11 +2200,11 @@
       </c>
       <c r="AE11" s="1">
         <f t="shared" si="14"/>
-        <v>114055.792</v>
+        <v>28513.947999999997</v>
       </c>
       <c r="AF11" s="26">
         <f t="shared" si="15"/>
-        <v>0.419364701176</v>
+        <v>0.41936470117599994</v>
       </c>
       <c r="AG11" s="1">
         <v>20</v>
@@ -2826,18 +2215,18 @@
       </c>
       <c r="AI11" s="1">
         <f t="shared" si="17"/>
-        <v>54400</v>
+        <v>13600</v>
       </c>
       <c r="AJ11" s="1">
         <f t="shared" si="18"/>
-        <v>59655.792</v>
+        <v>14913.947999999997</v>
       </c>
       <c r="AK11" s="26">
         <f t="shared" si="19"/>
-        <v>0.2193446991758</v>
+        <v>0.21934469917579991</v>
       </c>
     </row>
-    <row r="12" s="1" customFormat="1" ht="19" customHeight="1" spans="1:40">
+    <row r="12" spans="1:40" s="1" customFormat="1" ht="23" customHeight="1">
       <c r="A12" s="1" t="s">
         <v>37</v>
       </c>
@@ -2848,7 +2237,7 @@
         <v>7</v>
       </c>
       <c r="D12" s="10" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="E12" s="21" t="s">
         <v>40</v>
@@ -2856,132 +2245,129 @@
       <c r="F12" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="G12" s="11">
-        <v>100</v>
+      <c r="G12" s="27">
+        <v>10</v>
       </c>
       <c r="H12" s="1">
-        <v>99.99</v>
+        <v>59.99</v>
       </c>
       <c r="I12" s="22">
         <f t="shared" si="0"/>
-        <v>679.932</v>
+        <v>407.93200000000002</v>
       </c>
       <c r="J12" s="23">
         <v>6.8</v>
       </c>
       <c r="K12" s="22">
         <f t="shared" si="1"/>
-        <v>9999</v>
+        <v>599.9</v>
       </c>
       <c r="L12" s="1">
         <f t="shared" si="2"/>
-        <v>67993.2</v>
+        <v>4079.3199999999997</v>
       </c>
       <c r="M12" s="24">
-        <v>0.05</v>
+        <v>0.15</v>
       </c>
       <c r="N12" s="1">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="O12" s="1">
         <f t="shared" si="3"/>
-        <v>102</v>
+        <v>54.4</v>
       </c>
       <c r="P12" s="1">
         <f t="shared" si="4"/>
-        <v>10200</v>
+        <v>544</v>
       </c>
       <c r="Q12" s="1">
-        <v>178</v>
+        <v>135</v>
       </c>
       <c r="R12" s="1">
         <f t="shared" si="5"/>
-        <v>17800</v>
+        <v>1350</v>
       </c>
       <c r="S12" s="25">
         <f t="shared" si="6"/>
-        <v>0.26179088497085</v>
+        <v>0.33093750919270859</v>
       </c>
       <c r="T12" s="1">
-        <v>40</v>
+        <v>19</v>
       </c>
       <c r="U12" s="1">
         <f t="shared" si="7"/>
-        <v>4000</v>
+        <v>190</v>
       </c>
       <c r="V12" s="26">
         <f t="shared" si="8"/>
-        <v>0.058829412353</v>
+        <v>4.6576390182677507E-2</v>
       </c>
       <c r="W12" s="24">
         <v>0.06</v>
       </c>
       <c r="X12" s="1">
         <f t="shared" si="9"/>
-        <v>599.94</v>
+        <v>35.994</v>
       </c>
       <c r="Y12" s="1">
         <f t="shared" si="10"/>
-        <v>4079.592</v>
+        <v>244.75919999999999</v>
       </c>
       <c r="Z12" s="24">
         <v>0.05</v>
       </c>
       <c r="AA12" s="1">
         <f t="shared" si="11"/>
-        <v>499.95</v>
+        <v>29.995000000000001</v>
       </c>
       <c r="AB12" s="1">
         <f t="shared" si="12"/>
-        <v>3399.66</v>
+        <v>203.96600000000001</v>
       </c>
       <c r="AC12" s="1">
-        <v>5000</v>
+        <v>0</v>
       </c>
       <c r="AD12" s="1">
         <f t="shared" si="13"/>
-        <v>34000</v>
+        <v>0</v>
       </c>
       <c r="AE12" s="1">
         <f t="shared" si="14"/>
-        <v>28513.948</v>
+        <v>1546.5947999999999</v>
       </c>
       <c r="AF12" s="26">
         <f t="shared" si="15"/>
-        <v>0.419364701176</v>
-      </c>
-      <c r="AG12" s="1">
-        <v>20</v>
+        <v>0.37913054136473723</v>
       </c>
       <c r="AH12" s="1">
         <f t="shared" si="16"/>
-        <v>136</v>
+        <v>0</v>
       </c>
       <c r="AI12" s="1">
         <f t="shared" si="17"/>
-        <v>13600</v>
+        <v>0</v>
       </c>
       <c r="AJ12" s="1">
         <f t="shared" si="18"/>
-        <v>14913.948</v>
+        <v>1546.5947999999999</v>
       </c>
       <c r="AK12" s="26">
         <f t="shared" si="19"/>
-        <v>0.2193446991758</v>
+        <v>0.37913054136473723</v>
       </c>
     </row>
-    <row r="13" s="1" customFormat="1" ht="23" customHeight="1" spans="1:40">
-      <c r="A13" s="1" t="s">
+    <row r="13" spans="1:40" s="1" customFormat="1" ht="14.25" customHeight="1">
+      <c r="A13" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="B13" s="1" t="s">
+      <c r="B13" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="C13" s="1">
-        <v>7</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>46</v>
+      <c r="C13" s="28">
+        <v>8</v>
+      </c>
+      <c r="D13" s="9" t="s">
+        <v>39</v>
       </c>
       <c r="E13" s="21" t="s">
         <v>40</v>
@@ -2990,117 +2376,120 @@
         <v>41</v>
       </c>
       <c r="G13" s="27">
-        <v>10</v>
+        <v>300</v>
       </c>
       <c r="H13" s="1">
-        <v>59.99</v>
+        <v>99.99</v>
       </c>
       <c r="I13" s="22">
         <f t="shared" si="0"/>
-        <v>407.932</v>
+        <v>679.9319999999999</v>
       </c>
       <c r="J13" s="23">
         <v>6.8</v>
       </c>
       <c r="K13" s="22">
         <f t="shared" si="1"/>
-        <v>599.9</v>
+        <v>29997</v>
       </c>
       <c r="L13" s="1">
         <f t="shared" si="2"/>
-        <v>4079.32</v>
+        <v>203979.6</v>
       </c>
       <c r="M13" s="24">
-        <v>0.15</v>
+        <v>0.05</v>
       </c>
       <c r="N13" s="1">
-        <v>8</v>
+        <v>15</v>
       </c>
       <c r="O13" s="1">
         <f t="shared" si="3"/>
-        <v>54.4</v>
+        <v>102</v>
       </c>
       <c r="P13" s="1">
         <f t="shared" si="4"/>
-        <v>544</v>
+        <v>30600</v>
       </c>
       <c r="Q13" s="1">
-        <v>135</v>
+        <v>180</v>
       </c>
       <c r="R13" s="1">
         <f t="shared" si="5"/>
-        <v>1350</v>
+        <v>54000</v>
       </c>
       <c r="S13" s="25">
         <f t="shared" si="6"/>
-        <v>0.330937509192709</v>
+        <v>0.2647323555885</v>
       </c>
       <c r="T13" s="1">
-        <v>19</v>
+        <v>40</v>
       </c>
       <c r="U13" s="1">
         <f t="shared" si="7"/>
-        <v>190</v>
+        <v>12000</v>
       </c>
       <c r="V13" s="26">
         <f t="shared" si="8"/>
-        <v>0.0465763901826775</v>
+        <v>5.8829412353000002E-2</v>
       </c>
       <c r="W13" s="24">
         <v>0.06</v>
       </c>
       <c r="X13" s="1">
         <f t="shared" si="9"/>
-        <v>35.994</v>
+        <v>1799.82</v>
       </c>
       <c r="Y13" s="1">
         <f t="shared" si="10"/>
-        <v>244.7592</v>
+        <v>12238.776</v>
       </c>
       <c r="Z13" s="24">
         <v>0.05</v>
       </c>
       <c r="AA13" s="1">
         <f t="shared" si="11"/>
-        <v>29.995</v>
+        <v>1499.8500000000001</v>
       </c>
       <c r="AB13" s="1">
         <f t="shared" si="12"/>
-        <v>203.966</v>
+        <v>10198.980000000001</v>
       </c>
       <c r="AC13" s="1">
-        <v>0</v>
+        <v>5000</v>
       </c>
       <c r="AD13" s="1">
         <f t="shared" si="13"/>
-        <v>0</v>
+        <v>34000</v>
       </c>
       <c r="AE13" s="1">
         <f t="shared" si="14"/>
-        <v>1546.5948</v>
+        <v>84941.844000000012</v>
       </c>
       <c r="AF13" s="26">
         <f t="shared" si="15"/>
-        <v>0.379130541364737</v>
+        <v>0.41642323055835001</v>
+      </c>
+      <c r="AG13" s="1">
+        <v>20</v>
       </c>
       <c r="AH13" s="1">
         <f t="shared" si="16"/>
-        <v>0</v>
+        <v>136</v>
       </c>
       <c r="AI13" s="1">
         <f t="shared" si="17"/>
-        <v>0</v>
+        <v>40800</v>
       </c>
       <c r="AJ13" s="1">
         <f t="shared" si="18"/>
-        <v>1546.5948</v>
+        <v>44141.844000000012</v>
       </c>
       <c r="AK13" s="26">
         <f t="shared" si="19"/>
-        <v>0.379130541364737</v>
+        <v>0.21640322855814997</v>
       </c>
     </row>
-    <row r="14" s="1" customFormat="1" ht="14.25" customHeight="1" spans="1:40">
+    <row r="14" spans="1:40" s="1" customFormat="1" ht="14.25" customHeight="1">
       <c r="A14" s="28" t="s">
         <v>37</v>
       </c>
@@ -3111,7 +2500,7 @@
         <v>8</v>
       </c>
       <c r="D14" s="9" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
       <c r="E14" s="21" t="s">
         <v>40</v>
@@ -3120,25 +2509,25 @@
         <v>41</v>
       </c>
       <c r="G14" s="27">
-        <v>300</v>
+        <v>800</v>
       </c>
       <c r="H14" s="1">
         <v>99.99</v>
       </c>
       <c r="I14" s="22">
         <f t="shared" si="0"/>
-        <v>679.932</v>
+        <v>679.9319999999999</v>
       </c>
       <c r="J14" s="23">
         <v>6.8</v>
       </c>
       <c r="K14" s="22">
         <f t="shared" si="1"/>
-        <v>29997</v>
+        <v>79992</v>
       </c>
       <c r="L14" s="1">
         <f t="shared" si="2"/>
-        <v>203979.6</v>
+        <v>543945.6</v>
       </c>
       <c r="M14" s="24">
         <v>0.05</v>
@@ -3152,51 +2541,51 @@
       </c>
       <c r="P14" s="1">
         <f t="shared" si="4"/>
-        <v>30600</v>
+        <v>81600</v>
       </c>
       <c r="Q14" s="1">
         <v>180</v>
       </c>
       <c r="R14" s="1">
         <f t="shared" si="5"/>
-        <v>54000</v>
+        <v>144000</v>
       </c>
       <c r="S14" s="25">
         <f t="shared" si="6"/>
-        <v>0.2647323555885</v>
+        <v>0.26473235558850006</v>
       </c>
       <c r="T14" s="1">
         <v>40</v>
       </c>
       <c r="U14" s="1">
         <f t="shared" si="7"/>
-        <v>12000</v>
+        <v>32000</v>
       </c>
       <c r="V14" s="26">
         <f t="shared" si="8"/>
-        <v>0.058829412353</v>
+        <v>5.8829412353000009E-2</v>
       </c>
       <c r="W14" s="24">
         <v>0.06</v>
       </c>
       <c r="X14" s="1">
         <f t="shared" si="9"/>
-        <v>1799.82</v>
+        <v>4799.5199999999995</v>
       </c>
       <c r="Y14" s="1">
         <f t="shared" si="10"/>
-        <v>12238.776</v>
+        <v>32636.735999999997</v>
       </c>
       <c r="Z14" s="24">
         <v>0.05</v>
       </c>
       <c r="AA14" s="1">
         <f t="shared" si="11"/>
-        <v>1499.85</v>
+        <v>3999.6000000000004</v>
       </c>
       <c r="AB14" s="1">
         <f t="shared" si="12"/>
-        <v>10198.98</v>
+        <v>27197.280000000002</v>
       </c>
       <c r="AC14" s="1">
         <v>5000</v>
@@ -3207,11 +2596,11 @@
       </c>
       <c r="AE14" s="1">
         <f t="shared" si="14"/>
-        <v>84941.844</v>
+        <v>226511.58399999997</v>
       </c>
       <c r="AF14" s="26">
         <f t="shared" si="15"/>
-        <v>0.41642323055835</v>
+        <v>0.4164232305583499</v>
       </c>
       <c r="AG14" s="1">
         <v>20</v>
@@ -3222,18 +2611,18 @@
       </c>
       <c r="AI14" s="1">
         <f t="shared" si="17"/>
-        <v>40800</v>
+        <v>108800</v>
       </c>
       <c r="AJ14" s="1">
         <f t="shared" si="18"/>
-        <v>44141.844</v>
+        <v>117711.58399999997</v>
       </c>
       <c r="AK14" s="26">
         <f t="shared" si="19"/>
-        <v>0.21640322855815</v>
+        <v>0.21640322855814989</v>
       </c>
     </row>
-    <row r="15" s="1" customFormat="1" ht="14.25" customHeight="1" spans="1:40">
+    <row r="15" spans="1:40" s="1" customFormat="1" ht="19" customHeight="1">
       <c r="A15" s="28" t="s">
         <v>37</v>
       </c>
@@ -3243,8 +2632,8 @@
       <c r="C15" s="28">
         <v>8</v>
       </c>
-      <c r="D15" s="9" t="s">
-        <v>42</v>
+      <c r="D15" s="20" t="s">
+        <v>43</v>
       </c>
       <c r="E15" s="21" t="s">
         <v>40</v>
@@ -3253,25 +2642,25 @@
         <v>41</v>
       </c>
       <c r="G15" s="27">
-        <v>800</v>
+        <v>400</v>
       </c>
       <c r="H15" s="1">
         <v>99.99</v>
       </c>
       <c r="I15" s="22">
         <f t="shared" si="0"/>
-        <v>679.932</v>
+        <v>679.9319999999999</v>
       </c>
       <c r="J15" s="23">
         <v>6.8</v>
       </c>
       <c r="K15" s="22">
         <f t="shared" si="1"/>
-        <v>79992</v>
+        <v>39996</v>
       </c>
       <c r="L15" s="1">
         <f t="shared" si="2"/>
-        <v>543945.6</v>
+        <v>271972.8</v>
       </c>
       <c r="M15" s="24">
         <v>0.05</v>
@@ -3285,51 +2674,51 @@
       </c>
       <c r="P15" s="1">
         <f t="shared" si="4"/>
-        <v>81600</v>
+        <v>40800</v>
       </c>
       <c r="Q15" s="1">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="R15" s="1">
         <f t="shared" si="5"/>
-        <v>144000</v>
+        <v>71200</v>
       </c>
       <c r="S15" s="25">
         <f t="shared" si="6"/>
-        <v>0.2647323555885</v>
+        <v>0.26179088497085001</v>
       </c>
       <c r="T15" s="1">
         <v>40</v>
       </c>
       <c r="U15" s="1">
         <f t="shared" si="7"/>
-        <v>32000</v>
+        <v>16000</v>
       </c>
       <c r="V15" s="26">
         <f t="shared" si="8"/>
-        <v>0.058829412353</v>
+        <v>5.8829412353000009E-2</v>
       </c>
       <c r="W15" s="24">
         <v>0.06</v>
       </c>
       <c r="X15" s="1">
         <f t="shared" si="9"/>
-        <v>4799.52</v>
+        <v>2399.7599999999998</v>
       </c>
       <c r="Y15" s="1">
         <f t="shared" si="10"/>
-        <v>32636.736</v>
+        <v>16318.367999999999</v>
       </c>
       <c r="Z15" s="24">
         <v>0.05</v>
       </c>
       <c r="AA15" s="1">
         <f t="shared" si="11"/>
-        <v>3999.6</v>
+        <v>1999.8000000000002</v>
       </c>
       <c r="AB15" s="1">
         <f t="shared" si="12"/>
-        <v>27197.28</v>
+        <v>13598.640000000001</v>
       </c>
       <c r="AC15" s="1">
         <v>5000</v>
@@ -3340,11 +2729,11 @@
       </c>
       <c r="AE15" s="1">
         <f t="shared" si="14"/>
-        <v>226511.584</v>
+        <v>114055.79199999999</v>
       </c>
       <c r="AF15" s="26">
         <f t="shared" si="15"/>
-        <v>0.41642323055835</v>
+        <v>0.41936470117599994</v>
       </c>
       <c r="AG15" s="1">
         <v>20</v>
@@ -3355,18 +2744,18 @@
       </c>
       <c r="AI15" s="1">
         <f t="shared" si="17"/>
-        <v>108800</v>
+        <v>54400</v>
       </c>
       <c r="AJ15" s="1">
         <f t="shared" si="18"/>
-        <v>117711.584</v>
+        <v>59655.791999999987</v>
       </c>
       <c r="AK15" s="26">
         <f t="shared" si="19"/>
-        <v>0.21640322855815</v>
+        <v>0.21934469917579991</v>
       </c>
     </row>
-    <row r="16" s="1" customFormat="1" ht="19" customHeight="1" spans="1:40">
+    <row r="16" spans="1:40" s="1" customFormat="1" ht="19" customHeight="1">
       <c r="A16" s="28" t="s">
         <v>37</v>
       </c>
@@ -3377,7 +2766,7 @@
         <v>8</v>
       </c>
       <c r="D16" s="20" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="E16" s="21" t="s">
         <v>40</v>
@@ -3386,25 +2775,25 @@
         <v>41</v>
       </c>
       <c r="G16" s="27">
-        <v>400</v>
+        <v>500</v>
       </c>
       <c r="H16" s="1">
         <v>99.99</v>
       </c>
       <c r="I16" s="22">
         <f t="shared" si="0"/>
-        <v>679.932</v>
+        <v>679.9319999999999</v>
       </c>
       <c r="J16" s="23">
         <v>6.8</v>
       </c>
       <c r="K16" s="22">
         <f t="shared" si="1"/>
-        <v>39996</v>
+        <v>49995</v>
       </c>
       <c r="L16" s="1">
         <f t="shared" si="2"/>
-        <v>271972.8</v>
+        <v>339966</v>
       </c>
       <c r="M16" s="24">
         <v>0.05</v>
@@ -3418,51 +2807,51 @@
       </c>
       <c r="P16" s="1">
         <f t="shared" si="4"/>
-        <v>40800</v>
+        <v>51000</v>
       </c>
       <c r="Q16" s="1">
         <v>178</v>
       </c>
       <c r="R16" s="1">
         <f t="shared" si="5"/>
-        <v>71200</v>
+        <v>89000</v>
       </c>
       <c r="S16" s="25">
         <f t="shared" si="6"/>
-        <v>0.26179088497085</v>
+        <v>0.26179088497085001</v>
       </c>
       <c r="T16" s="1">
         <v>40</v>
       </c>
       <c r="U16" s="1">
         <f t="shared" si="7"/>
-        <v>16000</v>
+        <v>20000</v>
       </c>
       <c r="V16" s="26">
         <f t="shared" si="8"/>
-        <v>0.058829412353</v>
+        <v>5.8829412353000009E-2</v>
       </c>
       <c r="W16" s="24">
         <v>0.06</v>
       </c>
       <c r="X16" s="1">
         <f t="shared" si="9"/>
-        <v>2399.76</v>
+        <v>2999.7</v>
       </c>
       <c r="Y16" s="1">
         <f t="shared" si="10"/>
-        <v>16318.368</v>
+        <v>20397.96</v>
       </c>
       <c r="Z16" s="24">
         <v>0.05</v>
       </c>
       <c r="AA16" s="1">
         <f t="shared" si="11"/>
-        <v>1999.8</v>
+        <v>2499.75</v>
       </c>
       <c r="AB16" s="1">
         <f t="shared" si="12"/>
-        <v>13598.64</v>
+        <v>16998.3</v>
       </c>
       <c r="AC16" s="1">
         <v>5000</v>
@@ -3473,7 +2862,7 @@
       </c>
       <c r="AE16" s="1">
         <f t="shared" si="14"/>
-        <v>114055.792</v>
+        <v>142569.74000000002</v>
       </c>
       <c r="AF16" s="26">
         <f t="shared" si="15"/>
@@ -3488,416 +2877,289 @@
       </c>
       <c r="AI16" s="1">
         <f t="shared" si="17"/>
-        <v>54400</v>
+        <v>68000</v>
       </c>
       <c r="AJ16" s="1">
         <f t="shared" si="18"/>
-        <v>59655.792</v>
+        <v>74569.74000000002</v>
       </c>
       <c r="AK16" s="26">
         <f t="shared" si="19"/>
-        <v>0.2193446991758</v>
+        <v>0.21934469917579999</v>
       </c>
     </row>
-    <row r="17" s="1" customFormat="1" ht="19" customHeight="1" spans="1:37">
-      <c r="A17" s="28" t="s">
+    <row r="17" spans="1:37" ht="19" customHeight="1">
+      <c r="A17" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="B17" s="28" t="s">
+      <c r="B17" s="8" t="s">
         <v>38</v>
       </c>
-      <c r="C17" s="28">
+      <c r="C17" s="8">
         <v>8</v>
       </c>
       <c r="D17" s="20" t="s">
-        <v>44</v>
-      </c>
-      <c r="E17" s="21" t="s">
+        <v>45</v>
+      </c>
+      <c r="E17" s="10" t="s">
         <v>40</v>
       </c>
-      <c r="F17" s="21" t="s">
+      <c r="F17" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="G17" s="27">
-        <v>500</v>
-      </c>
-      <c r="H17" s="1">
+      <c r="G17" s="11">
+        <v>100</v>
+      </c>
+      <c r="H17" s="12">
         <v>99.99</v>
       </c>
-      <c r="I17" s="22">
+      <c r="I17" s="13">
         <f t="shared" si="0"/>
-        <v>679.932</v>
-      </c>
-      <c r="J17" s="23">
+        <v>679.9319999999999</v>
+      </c>
+      <c r="J17" s="14">
         <v>6.8</v>
       </c>
-      <c r="K17" s="22">
+      <c r="K17" s="13">
         <f t="shared" si="1"/>
-        <v>49995</v>
-      </c>
-      <c r="L17" s="1">
+        <v>9999</v>
+      </c>
+      <c r="L17" s="15">
         <f t="shared" si="2"/>
-        <v>339966</v>
-      </c>
-      <c r="M17" s="24">
+        <v>67993.2</v>
+      </c>
+      <c r="M17" s="16">
         <v>0.05</v>
       </c>
-      <c r="N17" s="1">
+      <c r="N17" s="12">
         <v>15</v>
       </c>
-      <c r="O17" s="1">
+      <c r="O17" s="12">
         <f t="shared" si="3"/>
         <v>102</v>
       </c>
-      <c r="P17" s="1">
+      <c r="P17" s="15">
         <f t="shared" si="4"/>
-        <v>51000</v>
-      </c>
-      <c r="Q17" s="1">
+        <v>10200</v>
+      </c>
+      <c r="Q17" s="15">
         <v>178</v>
       </c>
-      <c r="R17" s="1">
+      <c r="R17" s="15">
         <f t="shared" si="5"/>
-        <v>89000</v>
-      </c>
-      <c r="S17" s="25">
+        <v>17800</v>
+      </c>
+      <c r="S17" s="17">
         <f t="shared" si="6"/>
-        <v>0.26179088497085</v>
-      </c>
-      <c r="T17" s="1">
+        <v>0.26179088497085001</v>
+      </c>
+      <c r="T17" s="12">
         <v>40</v>
       </c>
-      <c r="U17" s="1">
+      <c r="U17" s="15">
         <f t="shared" si="7"/>
-        <v>20000</v>
-      </c>
-      <c r="V17" s="26">
+        <v>4000</v>
+      </c>
+      <c r="V17" s="18">
         <f t="shared" si="8"/>
-        <v>0.058829412353</v>
-      </c>
-      <c r="W17" s="24">
+        <v>5.8829412353000009E-2</v>
+      </c>
+      <c r="W17" s="16">
         <v>0.06</v>
       </c>
-      <c r="X17" s="1">
+      <c r="X17" s="12">
         <f t="shared" si="9"/>
-        <v>2999.7</v>
-      </c>
-      <c r="Y17" s="1">
+        <v>599.93999999999994</v>
+      </c>
+      <c r="Y17" s="19">
         <f t="shared" si="10"/>
-        <v>20397.96</v>
-      </c>
-      <c r="Z17" s="24">
+        <v>4079.5919999999996</v>
+      </c>
+      <c r="Z17" s="16">
         <v>0.05</v>
       </c>
-      <c r="AA17" s="1">
+      <c r="AA17" s="12">
         <f t="shared" si="11"/>
-        <v>2499.75</v>
-      </c>
-      <c r="AB17" s="1">
+        <v>499.95000000000005</v>
+      </c>
+      <c r="AB17" s="15">
         <f t="shared" si="12"/>
-        <v>16998.3</v>
-      </c>
-      <c r="AC17" s="1">
+        <v>3399.6600000000003</v>
+      </c>
+      <c r="AC17" s="12">
         <v>5000</v>
       </c>
-      <c r="AD17" s="1">
+      <c r="AD17" s="15">
         <f t="shared" si="13"/>
         <v>34000</v>
       </c>
-      <c r="AE17" s="1">
+      <c r="AE17" s="15">
         <f t="shared" si="14"/>
-        <v>142569.74</v>
-      </c>
-      <c r="AF17" s="26">
+        <v>28513.947999999997</v>
+      </c>
+      <c r="AF17" s="18">
         <f t="shared" si="15"/>
-        <v>0.419364701176</v>
-      </c>
-      <c r="AG17" s="1">
+        <v>0.41936470117599994</v>
+      </c>
+      <c r="AG17" s="12">
         <v>20</v>
       </c>
-      <c r="AH17" s="1">
+      <c r="AH17" s="12">
         <f t="shared" si="16"/>
         <v>136</v>
       </c>
-      <c r="AI17" s="1">
-        <f t="shared" si="17"/>
-        <v>68000</v>
-      </c>
-      <c r="AJ17" s="1">
-        <f t="shared" si="18"/>
-        <v>74569.74</v>
-      </c>
-      <c r="AK17" s="26">
-        <f t="shared" si="19"/>
-        <v>0.2193446991758</v>
-      </c>
-    </row>
-    <row r="18" ht="19" customHeight="1" spans="1:37">
-      <c r="A18" s="8" t="s">
-        <v>37</v>
-      </c>
-      <c r="B18" s="8" t="s">
-        <v>38</v>
-      </c>
-      <c r="C18" s="8">
-        <v>8</v>
-      </c>
-      <c r="D18" s="20" t="s">
-        <v>45</v>
-      </c>
-      <c r="E18" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="F18" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="G18" s="11">
-        <v>100</v>
-      </c>
-      <c r="H18" s="12">
-        <v>99.99</v>
-      </c>
-      <c r="I18" s="13">
-        <f t="shared" si="0"/>
-        <v>679.932</v>
-      </c>
-      <c r="J18" s="14">
-        <v>6.8</v>
-      </c>
-      <c r="K18" s="13">
-        <f t="shared" si="1"/>
-        <v>9999</v>
-      </c>
-      <c r="L18" s="15">
-        <f t="shared" si="2"/>
-        <v>67993.2</v>
-      </c>
-      <c r="M18" s="16">
-        <v>0.05</v>
-      </c>
-      <c r="N18" s="12">
-        <v>15</v>
-      </c>
-      <c r="O18" s="12">
-        <f t="shared" si="3"/>
-        <v>102</v>
-      </c>
-      <c r="P18" s="15">
-        <f t="shared" si="4"/>
-        <v>10200</v>
-      </c>
-      <c r="Q18" s="15">
-        <v>178</v>
-      </c>
-      <c r="R18" s="15">
-        <f t="shared" si="5"/>
-        <v>17800</v>
-      </c>
-      <c r="S18" s="17">
-        <f t="shared" si="6"/>
-        <v>0.26179088497085</v>
-      </c>
-      <c r="T18" s="12">
-        <v>40</v>
-      </c>
-      <c r="U18" s="15">
-        <f t="shared" si="7"/>
-        <v>4000</v>
-      </c>
-      <c r="V18" s="18">
-        <f t="shared" si="8"/>
-        <v>0.058829412353</v>
-      </c>
-      <c r="W18" s="16">
-        <v>0.06</v>
-      </c>
-      <c r="X18" s="12">
-        <f t="shared" si="9"/>
-        <v>599.94</v>
-      </c>
-      <c r="Y18" s="19">
-        <f t="shared" si="10"/>
-        <v>4079.592</v>
-      </c>
-      <c r="Z18" s="16">
-        <v>0.05</v>
-      </c>
-      <c r="AA18" s="12">
-        <f t="shared" si="11"/>
-        <v>499.95</v>
-      </c>
-      <c r="AB18" s="15">
-        <f t="shared" si="12"/>
-        <v>3399.66</v>
-      </c>
-      <c r="AC18" s="12">
-        <v>5000</v>
-      </c>
-      <c r="AD18" s="15">
-        <f t="shared" si="13"/>
-        <v>34000</v>
-      </c>
-      <c r="AE18" s="15">
-        <f t="shared" si="14"/>
-        <v>28513.948</v>
-      </c>
-      <c r="AF18" s="18">
-        <f t="shared" si="15"/>
-        <v>0.419364701176</v>
-      </c>
-      <c r="AG18" s="12">
-        <v>20</v>
-      </c>
-      <c r="AH18" s="12">
-        <f t="shared" si="16"/>
-        <v>136</v>
-      </c>
-      <c r="AI18" s="12">
+      <c r="AI17" s="12">
         <f t="shared" si="17"/>
         <v>13600</v>
       </c>
-      <c r="AJ18" s="12">
+      <c r="AJ17" s="12">
         <f t="shared" si="18"/>
-        <v>14913.948</v>
-      </c>
-      <c r="AK18" s="18">
+        <v>14913.947999999997</v>
+      </c>
+      <c r="AK17" s="18">
         <f t="shared" si="19"/>
-        <v>0.2193446991758</v>
+        <v>0.21934469917579991</v>
       </c>
     </row>
-    <row r="19" s="1" customFormat="1" ht="23" customHeight="1" spans="1:37">
-      <c r="A19" s="28" t="s">
+    <row r="18" spans="1:37" s="1" customFormat="1" ht="23" customHeight="1">
+      <c r="A18" s="28" t="s">
         <v>37</v>
       </c>
-      <c r="B19" s="28" t="s">
+      <c r="B18" s="28" t="s">
         <v>38</v>
       </c>
-      <c r="C19" s="28">
+      <c r="C18" s="28">
         <v>8</v>
       </c>
-      <c r="D19" s="9" t="s">
+      <c r="D18" s="9" t="s">
         <v>46</v>
       </c>
-      <c r="E19" s="21" t="s">
+      <c r="E18" s="21" t="s">
         <v>40</v>
       </c>
-      <c r="F19" s="21" t="s">
+      <c r="F18" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="G19" s="21">
+      <c r="G18" s="21">
         <v>10</v>
       </c>
-      <c r="H19" s="1">
+      <c r="H18" s="1">
         <v>59.99</v>
       </c>
-      <c r="I19" s="22">
+      <c r="I18" s="22">
         <f t="shared" si="0"/>
-        <v>407.932</v>
-      </c>
-      <c r="J19" s="23">
+        <v>407.93200000000002</v>
+      </c>
+      <c r="J18" s="23">
         <v>6.8</v>
       </c>
-      <c r="K19" s="22">
+      <c r="K18" s="22">
         <f t="shared" si="1"/>
         <v>599.9</v>
       </c>
-      <c r="L19" s="1">
+      <c r="L18" s="1">
         <f t="shared" si="2"/>
-        <v>4079.32</v>
-      </c>
-      <c r="M19" s="24">
+        <v>4079.3199999999997</v>
+      </c>
+      <c r="M18" s="24">
         <v>0.15</v>
       </c>
-      <c r="N19" s="1">
+      <c r="N18" s="1">
         <v>8</v>
       </c>
-      <c r="O19" s="1">
+      <c r="O18" s="1">
         <f t="shared" si="3"/>
         <v>54.4</v>
       </c>
-      <c r="P19" s="1">
+      <c r="P18" s="1">
         <f t="shared" si="4"/>
         <v>544</v>
       </c>
-      <c r="Q19" s="1">
+      <c r="Q18" s="1">
         <v>135</v>
       </c>
-      <c r="R19" s="1">
+      <c r="R18" s="1">
         <f t="shared" si="5"/>
         <v>1350</v>
       </c>
-      <c r="S19" s="25">
+      <c r="S18" s="25">
         <f t="shared" si="6"/>
-        <v>0.330937509192709</v>
-      </c>
-      <c r="T19" s="1">
+        <v>0.33093750919270859</v>
+      </c>
+      <c r="T18" s="1">
         <v>19</v>
       </c>
-      <c r="U19" s="1">
+      <c r="U18" s="1">
         <f t="shared" si="7"/>
         <v>190</v>
       </c>
-      <c r="V19" s="26">
+      <c r="V18" s="26">
         <f t="shared" si="8"/>
-        <v>0.0465763901826775</v>
-      </c>
-      <c r="W19" s="24">
+        <v>4.6576390182677507E-2</v>
+      </c>
+      <c r="W18" s="24">
         <v>0.06</v>
       </c>
-      <c r="X19" s="1">
+      <c r="X18" s="1">
         <f t="shared" si="9"/>
         <v>35.994</v>
       </c>
-      <c r="Y19" s="1">
+      <c r="Y18" s="1">
         <f t="shared" si="10"/>
-        <v>244.7592</v>
-      </c>
-      <c r="Z19" s="24">
+        <v>244.75919999999999</v>
+      </c>
+      <c r="Z18" s="24">
         <v>0.05</v>
       </c>
-      <c r="AA19" s="1">
+      <c r="AA18" s="1">
         <f t="shared" si="11"/>
-        <v>29.995</v>
-      </c>
-      <c r="AB19" s="1">
+        <v>29.995000000000001</v>
+      </c>
+      <c r="AB18" s="1">
         <f t="shared" si="12"/>
-        <v>203.966</v>
-      </c>
-      <c r="AC19" s="1">
+        <v>203.96600000000001</v>
+      </c>
+      <c r="AC18" s="1">
         <v>0</v>
       </c>
-      <c r="AD19" s="1">
+      <c r="AD18" s="1">
         <f t="shared" si="13"/>
         <v>0</v>
       </c>
-      <c r="AE19" s="1">
+      <c r="AE18" s="1">
         <f t="shared" si="14"/>
-        <v>1546.5948</v>
-      </c>
-      <c r="AF19" s="26">
+        <v>1546.5947999999999</v>
+      </c>
+      <c r="AF18" s="26">
         <f t="shared" si="15"/>
-        <v>0.379130541364737</v>
-      </c>
-      <c r="AH19" s="1">
+        <v>0.37913054136473723</v>
+      </c>
+      <c r="AH18" s="1">
         <f t="shared" si="16"/>
         <v>0</v>
       </c>
-      <c r="AI19" s="1">
+      <c r="AI18" s="1">
         <f t="shared" si="17"/>
         <v>0</v>
       </c>
-      <c r="AJ19" s="1">
+      <c r="AJ18" s="1">
         <f t="shared" si="18"/>
-        <v>1546.5948</v>
-      </c>
-      <c r="AK19" s="26">
+        <v>1546.5947999999999</v>
+      </c>
+      <c r="AK18" s="26">
         <f t="shared" si="19"/>
-        <v>0.379130541364737</v>
+        <v>0.37913054136473723</v>
+      </c>
+    </row>
+    <row r="19" spans="1:37" ht="14" customHeight="1">
+      <c r="G19" s="1">
+        <f>SUM(G2:G18)</f>
+        <v>6330</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <headerFooter/>
-  <legacyDrawing r:id="rId2"/>
+  <legacyDrawing r:id="rId1"/>
 </worksheet>
 </file>
--- a/_business-operations/sales-forecast/tk6-8月销售计划.xlsx
+++ b/_business-operations/sales-forecast/tk6-8月销售计划.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/qisanjiudekeaiduo/Downloads/python3/Harlottecc/_business-operations/sales-forecast/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{87EE9439-0F3F-824B-BDBC-70FF2083423D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8934F76E-3558-984A-BBF9-5411DFF93286}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="720" windowWidth="29400" windowHeight="18400" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
